--- a/docs/settlements_data_dictionary.xlsx
+++ b/docs/settlements_data_dictionary.xlsx
@@ -1110,7 +1110,7 @@
     <row r="42" ht="68.25" customHeight="1" s="6">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Cooling Demand</t>
+          <t>Agricultural Cooling Potential</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -1120,75 +1120,75 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of market accessibility to export markets. Weighted average of nearby population, travel times to capital city, nearest cities, airports,ports, railway stations (0=lowest, 1=highest)</t>
+          <t>Composite indicator of farming activity. Weighted average of nearby population, travel times to capital city, nearest cities, airports,ports, railway stations (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="41.25" customHeight="1" s="6">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Cooling Demand</t>
+          <t>Agricultural Cooling Potential</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Ag Cooling Demand Export Market</t>
+          <t>Ag Cooling Potential Export Market</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling demand for fish products destined for export markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling potential for agricultural products destined for export markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="41.25" customHeight="1" s="6">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Cooling Demand</t>
+          <t>Agricultural Cooling Potential</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Ag Cooling Demand National Market</t>
+          <t>Ag Cooling Potential National Market</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling demand for fish products destined for national distribution (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling potential for agricultural products destined for national distribution (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="41.25" customHeight="1" s="6">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Cooling Demand</t>
+          <t>Agricultural Cooling Potential</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Ag Cooling Demand Fresh Markets</t>
+          <t>Ag Cooling Potential Fresh Markets</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling demand for fish products destined for local fresh markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling potential for agricultural products destined for local fresh markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="41.25" customHeight="1" s="6">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Agricultural Cooling Demand</t>
+          <t>Agricultural Cooling Potential</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Ag Cooling Demand ALL Markets</t>
+          <t>Ag Cooling Potential ALL Markets</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling demand for fish products across all destination markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling potential for agricultural products across all destination markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
@@ -1380,34 +1380,34 @@
       </c>
     </row>
     <row r="58" ht="68.25" customHeight="1" s="6">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Fishing Cooling Demand</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Fishing Cooling Potential</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Fishing Activity (Marine)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Sub-index of marine fishing activity based on distance to the coastline (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1" s="6">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Fishing Cooling Demand</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Fishing Cooling Potential</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Fishing Activity (Inland)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Sub-index of inland fishing activity based on availability of permanent water within 10km (0=lowest, 1=highest)</t>
         </is>
@@ -1416,7 +1416,7 @@
     <row r="60" ht="41.25" customHeight="1" s="6">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="61" ht="41.25" customHeight="1" s="6">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -1450,68 +1450,68 @@
     <row r="62" ht="41.25" customHeight="1" s="6">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Fish Cooling Demand Export Market</t>
+          <t>Fish Cooling Potential Export Market</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling/ice making demand for fish products destined for export markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling/ice making potential for fish products destined for export markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="41.25" customHeight="1" s="6">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Fish Cooling Demand National Market</t>
+          <t>Fish Cooling Potential National Market</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling/ice making demand for fish products destined for national distribution (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling/ice making potential for fish products destined for national distribution (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="27.75" customHeight="1" s="6">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Fish Cooling Demand Fresh Markets</t>
+          <t>Fish Cooling Potential Fresh Markets</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling/ice making demand for fish products destined for local fresh markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling/ice making potential for fish products destined for local fresh markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Fishing Cooling Demand</t>
+          <t>Fishing Cooling Potential</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Fish Cooling Demand ALL Markets</t>
+          <t>Fish Cooling Potential ALL Markets</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Composite indicator of cooling/ice making demand for fish products across all destination markets (0=lowest, 1=highest)</t>
+          <t>Composite indicator of cooling/ice making potential for fish products across all destination markets (0=lowest, 1=highest)</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
     <row r="42" ht="68.65000000000001" customHeight="1" s="6">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération agricole</t>
+          <t>Potentiel de réfrigération agricole</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2297,68 +2297,68 @@
     <row r="43" ht="55.2" customHeight="1" s="6">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération agricole</t>
+          <t>Potentiel de réfrigération agricole</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Agri. Marché Export</t>
+          <t>Potentiel Refroid. Agri. Marché Export</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération pour les produits agricoles destinés aux marchés d'exportation (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération pour les produits agricoles destinés aux marchés d'exportation (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="55.2" customHeight="1" s="6">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération agricole</t>
+          <t>Potentiel de réfrigération agricole</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Agri. Marché National</t>
+          <t>Potentiel Refroid. Agri. Marché National</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération pour les produits agricoles destinés à la distribution nationale (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération pour les produits agricoles destinés à la distribution nationale (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="55.2" customHeight="1" s="6">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération agricole</t>
+          <t>Potentiel de réfrigération agricole</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Agri. Marchés Frais</t>
+          <t>Potentiel Refroid. Agri. Marchés Frais</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération pour les produits agricoles destinés aux marchés frais locaux (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération pour les produits agricoles destinés aux marchés frais locaux (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="55.2" customHeight="1" s="6">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération agricole</t>
+          <t>Potentiel de réfrigération agricole</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Agri. TOUS Marchés</t>
+          <t>Potentiel Refroid. Agri. TOUS Marchés</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération pour les produits agricoles sur l'ensemble des marchés de destination (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération pour les produits agricoles sur l'ensemble des marchés de destination (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
@@ -2550,34 +2550,34 @@
       </c>
     </row>
     <row r="58" ht="82.05" customHeight="1" s="6">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Demande de réfrigération pour la pêche</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Potentiel de réfrigération pour la pêche</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Activité de pêche (Marine)</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Sous-indice de l'activité de pêche marine basé sur la distance à la côte (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="28.35" customHeight="1" s="6">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Demande de réfrigération pour la pêche</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Potentiel de réfrigération pour la pêche</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Activité de pêche (Continentale)</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Sous-indice de l'activité de pêche continentale basé sur la disponibilité d'eau permanente dans un rayon de 10 km (0=le plus bas, 1=le plus élevé)</t>
         </is>
@@ -2586,7 +2586,7 @@
     <row r="60" ht="55.2" customHeight="1" s="6">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="61" ht="55.2" customHeight="1" s="6">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -2620,68 +2620,68 @@
     <row r="62" ht="55.2" customHeight="1" s="6">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Pêche Marché Export</t>
+          <t>Potentiel Refroid. Pêche Marché Export</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération/fabrication de glace pour les produits de la pêche destinés aux marchés d'exportation (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération/fabrication de glace pour les produits de la pêche destinés aux marchés d'exportation (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="63" ht="55.2" customHeight="1" s="6">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Pêche Marché National</t>
+          <t>Potentiel Refroid. Pêche Marché National</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération/fabrication de glace pour les produits de la pêche destinés à la distribution nationale (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération/fabrication de glace pour les produits de la pêche destinés à la distribution nationale (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="27.75" customHeight="1" s="6">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Pêche Marchés Frais</t>
+          <t>Potentiel Refroid. Pêche Marchés Frais</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération/fabrication de glace pour les produits de la pêche destinés aux marchés frais locaux (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération/fabrication de glace pour les produits de la pêche destinés aux marchés frais locaux (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Demande de réfrigération pour la pêche</t>
+          <t>Potentiel de réfrigération pour la pêche</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Demande Refroid. Pêche TOUS Marchés</t>
+          <t>Potentiel Refroid. Pêche TOUS Marchés</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Indicateur composite de la demande de réfrigération/fabrication de glace pour les produits de la pêche sur l'ensemble des marchés de destination (0=le plus bas, 1=le plus élevé)</t>
+          <t>Indicateur composite du potentiel de réfrigération/fabrication de glace pour les produits de la pêche sur l'ensemble des marchés de destination (0=le plus bas, 1=le plus élevé)</t>
         </is>
       </c>
     </row>
